--- a/docs/Project_Version_History.xlsx
+++ b/docs/Project_Version_History.xlsx
@@ -431,27 +431,27 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Version</t>
+          <t>Version (Major.Minor.Build)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Release Date</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Git Push ID</t>
+          <t>Git Commit Range</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Major Changes</t>
+          <t>Major Changes Overview</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Functional Changes</t>
+          <t>Functional / Logic Changes</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -461,17 +461,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Database/API Changes</t>
+          <t>Database / API / Backend Changes</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bugs Fixed</t>
+          <t>Bugs / Issues Fixed</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Testing Status</t>
+          <t>QA / Testing Status</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Limitations / Pending Work</t>
         </is>
       </c>
     </row>
@@ -511,16 +511,8 @@
           <t>Updated the intent router to strip conversational fluff like "where is" to properly extract book titles. Removed hardcoded entrance fallback so the system forcefully prompts users for their location before initiating a route.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Fixed catalog lookup failing on "where is" questions.</t>
@@ -573,11 +565,7 @@
           <t>Updated map and navigation panel</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
@@ -626,11 +614,7 @@
           <t>Updated map and navigation panel</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
@@ -674,11 +658,7 @@
           <t>Updated GROQ_MODEL in config.py from llama-3.1-8b-instant (which returned 404) to llama3-8b-8192 to resolve API failures.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Changed Groq Model endpoints</t>
@@ -736,11 +716,7 @@
           <t>Updated map and navigation panel</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Fixed "Too many active WebGL contexts" memory leak. Fixed Groq 400 decommission error.</t>
@@ -788,11 +764,7 @@
           <t>Wrote a script to query the allowed models on the user's specific Groq API key tier, and updated config.py to use qwen/qwen3.6-27b which was confirmed to work and support thinking blocks.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Changed Groq Model endpoints</t>

--- a/docs/Project_Version_History.xlsx
+++ b/docs/Project_Version_History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,51 @@
           <t>Limitations / Pending Work</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Git Push ID</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Major Changes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Functional Changes</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Database/API Changes</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Bugs Fixed</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Testing Status</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -533,6 +578,15 @@
           <t>Deployed via Railway</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -582,6 +636,15 @@
           <t>Deployed via Railway</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -631,6 +694,15 @@
           <t>Deployed via Railway</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -684,6 +756,15 @@
           <t>Deployed via Railway</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -737,6 +818,15 @@
           <t>Deployed via Railway</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -786,6 +876,81 @@
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>Deployed via Railway</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Added AI Chat Logs tab and Voice greeting logic.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Live / Deployed</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5.1.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>237b894</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Completed Books API, Analytics Dashboard, and Real-time SQL Sync</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Created fully working Books API so Admin UI can Add/Edit/Delete books. Added AI Chat Audit Log and Analytics Dashboard (showing Top Missing Books). Modified the RAG search engine to directly query the live SQLite database first, bypassing ChromaDB for exact titles, which fixes the stale data bug and drops search latency to milliseconds. Added time-based Voice Assistant greeting.</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>New analytics_routes and book_routes APIs. RAG engine modified to hit SQLite.</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Fixed stale book location data by querying live DB. Reduced agent latency. Added missing Voice greeting.</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Verified SQL query execution in search_catalog.</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>Deployed via Railway</t>
         </is>

--- a/docs/Project_Version_History.xlsx
+++ b/docs/Project_Version_History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -956,6 +956,68 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Created Settings Panel for Admin.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Live / Deployed</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5.2.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Completed Phase 3: Global Library Settings Injection</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Added library_name, opening_hours, and library_policies to the LibraryConfig database schema. Built the Settings.jsx UI panel for admins to edit these fields. Modified the core AI RAG engine (engine.py) to dynamically query these settings from the live database and inject them directly into the LLM System Prompt. The Voice AI will now enforce custom library rules globally.</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Modified LibraryConfig schema with auto-migration.</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Verified UI saves correctly to DB and engine retrieves it.</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Deployed via Railway</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Project_Version_History.xlsx
+++ b/docs/Project_Version_History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,6 +1018,68 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Added Add User modal to Users.jsx</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Live / Deployed</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5.3.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4b71756</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Completed Phase 4: Users and Departments Management</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Added a Create User modal to Users.jsx allowing Admins to register new users or other admins. Verified that Departments.jsx is fully functional for tracking campus buildings, HODs, and floors.</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Integrated register API into Admin dashboard.</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Verified UI rendering.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Deployed via Railway</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Project_Version_History.xlsx
+++ b/docs/Project_Version_History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,6 +1080,68 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Animated dashed lines, CSV Export button, Settings voice dropdown.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Live / Deployed</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6.0.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>9173e3f</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Completed Phase 6, 7, 8, 9</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Verified Text Chat UI functionality. Added AI Voice preset customization (Aria, Guy, Sonia, Neerja, Natasha) to the database and Settings.jsx. Integrated selected voice with edge-tts in main.py. Added an animated dashed texture effect to the 3D map route line in LibraryWayfinder.jsx. Added an Export CSV button to Analytics.jsx to download missing books data.</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Modified LibraryConfig with voice_preset column.</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Verified UI rendering.</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Deployed via Railway</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
